--- a/results/overall_results_2050.xlsx
+++ b/results/overall_results_2050.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B17B893-40E6-4FA6-8327-C036CF67AC7F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E533391C-1097-4D38-B6E0-3A022826588E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="14370" windowHeight="8715" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="climate_change_1-step_vs_5-step" sheetId="15" r:id="rId1"/>
@@ -1681,7 +1681,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="4">
-        <v>0.75578589809279861</v>
+        <v>0.41725000000000001</v>
       </c>
       <c r="D2" s="4">
         <v>4.7000672476377415E-3</v>
@@ -1700,13 +1700,13 @@
       </c>
       <c r="I2" s="4">
         <f>SUM(C2:H2)</f>
-        <v>0.79549004358150621</v>
+        <v>0.45695414548870761</v>
       </c>
       <c r="J2" s="1">
-        <v>0.68200000000000005</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.90900000000000003</v>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0.52</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1718,7 +1718,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="4">
-        <v>0.82596248023182151</v>
+        <v>0.4559898407256347</v>
       </c>
       <c r="D3" s="4">
         <v>5.1168474233421232E-2</v>
@@ -1737,13 +1737,13 @@
       </c>
       <c r="I3" s="4">
         <f>SUM(C3:H3)</f>
-        <v>1.0251582075153876</v>
+        <v>0.65518556800920069</v>
       </c>
       <c r="J3" s="1">
-        <v>0.90100000000000002</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="K3" s="1">
-        <v>1.149</v>
+        <v>0.72399999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -2041,7 +2041,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="4">
-        <v>0.75578589809279861</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
@@ -2066,13 +2066,13 @@
       </c>
       <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
-        <v>0.79549004358150621</v>
+        <v>0.45670414548870758</v>
       </c>
       <c r="L2" s="1">
-        <v>0.68200000000000005</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0.90900000000000003</v>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0.52</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="4">
-        <v>0.154</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="E3" s="4">
         <v>1.4572960426533341</v>
@@ -2109,13 +2109,13 @@
       </c>
       <c r="K3" s="4">
         <f>SUM(C3:J3)</f>
-        <v>1.6713312871430615</v>
+        <v>1.6023312871430615</v>
       </c>
       <c r="L3" s="1">
-        <v>1.643</v>
+        <v>1.587</v>
       </c>
       <c r="M3" s="1">
-        <v>1.782</v>
+        <v>1.663</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
@@ -2177,27 +2177,27 @@
         <v>0.23</v>
       </c>
       <c r="E5" s="4">
-        <f>E3</f>
+        <f t="shared" ref="E5:J5" si="1">E3</f>
         <v>1.4572960426533341</v>
       </c>
       <c r="F5" s="4">
-        <f>F3</f>
+        <f t="shared" si="1"/>
         <v>8.2759901362157908E-3</v>
       </c>
       <c r="G5" s="4">
-        <f>G3</f>
+        <f t="shared" si="1"/>
         <v>1.3848836761850409E-2</v>
       </c>
       <c r="H5" s="4">
-        <f>H3</f>
+        <f t="shared" si="1"/>
         <v>1.4293923222371456E-3</v>
       </c>
       <c r="I5" s="4">
-        <f>I3</f>
+        <f t="shared" si="1"/>
         <v>3.6481025269424254E-2</v>
       </c>
       <c r="J5" s="4">
-        <f>J3</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K5" s="4">
@@ -2448,7 +2448,7 @@
         <v>19</v>
       </c>
       <c r="C2" s="4">
-        <v>1.5218623269028277</v>
+        <v>0.84017588771828156</v>
       </c>
       <c r="D2" s="4">
         <v>0</v>
@@ -2473,15 +2473,15 @@
       </c>
       <c r="K2" s="4">
         <f>SUM(C2:J2)</f>
-        <v>1.5218623269028277</v>
+        <v>0.84017588771828156</v>
       </c>
       <c r="L2" s="4">
         <f>K2*0.8</f>
-        <v>1.2174898615222622</v>
+        <v>0.67214071017462529</v>
       </c>
       <c r="M2" s="4">
         <f>K2*1.2</f>
-        <v>1.8262347922833932</v>
+        <v>1.0082110652619378</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="18" x14ac:dyDescent="0.35">
@@ -2499,7 +2499,7 @@
         <v>0.66279646911249523</v>
       </c>
       <c r="E3" s="4">
-        <v>0.37789526744500879</v>
+        <v>0.217</v>
       </c>
       <c r="F3" s="4">
         <v>0</v>
@@ -2518,13 +2518,13 @@
       </c>
       <c r="K3" s="4">
         <f>SUM(C3:J3)</f>
-        <v>1.1666697923001919</v>
+        <v>1.0057745248551828</v>
       </c>
       <c r="L3" s="4">
-        <v>1.113</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="M3" s="4">
-        <v>1.2210000000000001</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="18" x14ac:dyDescent="0.35">
@@ -2545,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4">
-        <v>0.80069999999999997</v>
+        <v>0.76737994916082408</v>
       </c>
       <c r="G4" s="4">
         <v>4.2341987290915609E-2</v>
@@ -2561,13 +2561,13 @@
       </c>
       <c r="K4" s="4">
         <f>SUM(C4:J4)</f>
-        <v>1.6490532637253097</v>
+        <v>1.6157332128861337</v>
       </c>
       <c r="L4" s="4">
-        <v>1.635</v>
+        <v>1.609</v>
       </c>
       <c r="M4" s="4">
-        <v>1.702</v>
+        <v>1.645</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="18" x14ac:dyDescent="0.35">
